--- a/deliverables/2-mechanism-design/Aurumix_ICS_Score_Calculator.xlsx
+++ b/deliverables/2-mechanism-design/Aurumix_ICS_Score_Calculator.xlsx
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -847,55 +847,55 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>IF(B18&lt;=$B$129,B18*50/$B$129,IF(B18&gt;=$B$130,100,50+(B18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B18&lt;=$B$130,B18*50/$B$130,IF(B18&gt;=$B$131,100,50+(B18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>IF(C18&lt;=$B$129,C18*50/$B$129,IF(C18&gt;=$B$130,100,50+(C18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C18&lt;=$B$130,C18*50/$B$130,IF(C18&gt;=$B$131,100,50+(C18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(D18&lt;=$B$129,D18*50/$B$129,IF(D18&gt;=$B$130,100,50+(D18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(D18&lt;=$B$130,D18*50/$B$130,IF(D18&gt;=$B$131,100,50+(D18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(E18&lt;=$B$129,E18*50/$B$129,IF(E18&gt;=$B$130,100,50+(E18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(E18&lt;=$B$130,E18*50/$B$130,IF(E18&gt;=$B$131,100,50+(E18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>IF(F18&lt;=$B$129,F18*50/$B$129,IF(F18&gt;=$B$130,100,50+(F18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(F18&lt;=$B$130,F18*50/$B$130,IF(F18&gt;=$B$131,100,50+(F18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>IF(G18&lt;=$B$129,G18*50/$B$129,IF(G18&gt;=$B$130,100,50+(G18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(G18&lt;=$B$130,G18*50/$B$130,IF(G18&gt;=$B$131,100,50+(G18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>IF(H18&lt;=$B$129,H18*50/$B$129,IF(H18&gt;=$B$130,100,50+(H18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(H18&lt;=$B$130,H18*50/$B$130,IF(H18&gt;=$B$131,100,50+(H18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="I19" s="13">
-        <f>IF(I18&lt;=$B$129,I18*50/$B$129,IF(I18&gt;=$B$130,100,50+(I18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(I18&lt;=$B$130,I18*50/$B$130,IF(I18&gt;=$B$131,100,50+(I18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="J19" s="13">
-        <f>IF(J18&lt;=$B$129,J18*50/$B$129,IF(J18&gt;=$B$130,100,50+(J18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(J18&lt;=$B$130,J18*50/$B$130,IF(J18&gt;=$B$131,100,50+(J18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="K19" s="13">
-        <f>IF(K18&lt;=$B$129,K18*50/$B$129,IF(K18&gt;=$B$130,100,50+(K18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(K18&lt;=$B$130,K18*50/$B$130,IF(K18&gt;=$B$131,100,50+(K18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="L19" s="13">
-        <f>IF(L18&lt;=$B$129,L18*50/$B$129,IF(L18&gt;=$B$130,100,50+(L18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(L18&lt;=$B$130,L18*50/$B$130,IF(L18&gt;=$B$131,100,50+(L18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="M19" s="13">
-        <f>IF(M18&lt;=$B$129,M18*50/$B$129,IF(M18&gt;=$B$130,100,50+(M18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(M18&lt;=$B$130,M18*50/$B$130,IF(M18&gt;=$B$131,100,50+(M18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="N19" s="13">
-        <f>IF(N18&lt;=$B$129,N18*50/$B$129,IF(N18&gt;=$B$130,100,50+(N18-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(N18&lt;=$B$130,N18*50/$B$130,IF(N18&gt;=$B$131,100,50+(N18-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
     </row>
@@ -989,55 +989,55 @@
         </is>
       </c>
       <c r="B27" s="13">
-        <f>MIN(B26,$B$131)*100/$B$131</f>
+        <f>MIN(B26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="C27" s="13">
-        <f>MIN(C26,$B$131)*100/$B$131</f>
+        <f>MIN(C26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>MIN(D26,$B$131)*100/$B$131</f>
+        <f>MIN(D26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>MIN(E26,$B$131)*100/$B$131</f>
+        <f>MIN(E26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="F27" s="13">
-        <f>MIN(F26,$B$131)*100/$B$131</f>
+        <f>MIN(F26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G27" s="13">
-        <f>MIN(G26,$B$131)*100/$B$131</f>
+        <f>MIN(G26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H27" s="13">
-        <f>MIN(H26,$B$131)*100/$B$131</f>
+        <f>MIN(H26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="I27" s="13">
-        <f>MIN(I26,$B$131)*100/$B$131</f>
+        <f>MIN(I26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="J27" s="13">
-        <f>MIN(J26,$B$131)*100/$B$131</f>
+        <f>MIN(J26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="K27" s="13">
-        <f>MIN(K26,$B$131)*100/$B$131</f>
+        <f>MIN(K26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="L27" s="13">
-        <f>MIN(L26,$B$131)*100/$B$131</f>
+        <f>MIN(L26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="M27" s="13">
-        <f>MIN(M26,$B$131)*100/$B$131</f>
+        <f>MIN(M26,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="N27" s="13">
-        <f>MIN(N26,$B$131)*100/$B$131</f>
+        <f>MIN(N26,$B$132)*100/$B$132</f>
         <v/>
       </c>
     </row>
@@ -1140,47 +1140,47 @@
         </is>
       </c>
       <c r="B38" s="16">
-        <f>IF(B37&lt;=$B$132,1,MAX(0,1-(B37-$B$132)/(1-$B$132)))</f>
+        <f>IF(B37&lt;=$B$133,1,MAX(0,1-(B37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>IF(C37&lt;=$B$132,1,MAX(0,1-(C37-$B$132)/(1-$B$132)))</f>
+        <f>IF(C37&lt;=$B$133,1,MAX(0,1-(C37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>IF(D37&lt;=$B$132,1,MAX(0,1-(D37-$B$132)/(1-$B$132)))</f>
+        <f>IF(D37&lt;=$B$133,1,MAX(0,1-(D37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>IF(E37&lt;=$B$132,1,MAX(0,1-(E37-$B$132)/(1-$B$132)))</f>
+        <f>IF(E37&lt;=$B$133,1,MAX(0,1-(E37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>IF(F37&lt;=$B$132,1,MAX(0,1-(F37-$B$132)/(1-$B$132)))</f>
+        <f>IF(F37&lt;=$B$133,1,MAX(0,1-(F37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>IF(G37&lt;=$B$132,1,MAX(0,1-(G37-$B$132)/(1-$B$132)))</f>
+        <f>IF(G37&lt;=$B$133,1,MAX(0,1-(G37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>IF(H37&lt;=$B$132,1,MAX(0,1-(H37-$B$132)/(1-$B$132)))</f>
+        <f>IF(H37&lt;=$B$133,1,MAX(0,1-(H37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>IF(I37&lt;=$B$132,1,MAX(0,1-(I37-$B$132)/(1-$B$132)))</f>
+        <f>IF(I37&lt;=$B$133,1,MAX(0,1-(I37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>IF(J37&lt;=$B$132,1,MAX(0,1-(J37-$B$132)/(1-$B$132)))</f>
+        <f>IF(J37&lt;=$B$133,1,MAX(0,1-(J37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(K37&lt;=$B$132,1,MAX(0,1-(K37-$B$132)/(1-$B$132)))</f>
+        <f>IF(K37&lt;=$B$133,1,MAX(0,1-(K37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="L38" s="16">
-        <f>IF(L37&lt;=$B$132,1,MAX(0,1-(L37-$B$132)/(1-$B$132)))</f>
+        <f>IF(L37&lt;=$B$133,1,MAX(0,1-(L37-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>No tier</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>You have opened an account.</t>
+          <t>Account open, gate not yet passed. No score is calculated.</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Six payments made. You are established, permanently.</t>
+          <t>Six months straight. You are established, permanently.</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
@@ -1402,172 +1402,134 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>The gate comes first: six consecutive payments before any score exists. Everyone enters at Silver, 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
           <t>Silver is permanent. Every tier above it is rented by conduct — which is the point.</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
     <row r="59"/>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="60"/>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  A WORKED STORY   —   Rajesh, USD 75 a month</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>One missed payment and one real withdrawal, across five years. Follow the last two columns.</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>When</t>
         </is>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B64" s="21" t="inlineStr">
         <is>
           <t>What happened</t>
         </is>
       </c>
-      <c r="C63" s="21" t="inlineStr">
+      <c r="C64" s="21" t="inlineStr">
         <is>
           <t>Months</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
+      <c r="D64" s="21" t="inlineStr">
         <is>
           <t>of last 12</t>
         </is>
       </c>
-      <c r="E63" s="21" t="inlineStr">
+      <c r="E64" s="21" t="inlineStr">
         <is>
           <t>Sold</t>
         </is>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="F64" s="21" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="G63" s="21" t="inlineStr">
+      <c r="G64" s="21" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="H63" s="21" t="inlineStr">
+      <c r="H64" s="21" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="I63" s="21" t="inlineStr">
+      <c r="I64" s="21" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
-      <c r="J63" s="21" t="inlineStr"/>
-      <c r="K63" s="21" t="inlineStr">
+      <c r="J64" s="21" t="inlineStr"/>
+      <c r="K64" s="21" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>Month 1</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Opens an account, first payment clears.</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="26">
-        <f>IF(C64&lt;=$B$129,C64*50/$B$129,IF(C64&gt;=$B$130,100,50+(C64-$B$129)*50/($B$130-$B$129)))</f>
-        <v/>
-      </c>
-      <c r="G64" s="26">
-        <f>MIN(D64,$B$131)*100/$B$131</f>
-        <v/>
-      </c>
-      <c r="H64" s="27">
-        <f>IF(E64&lt;=$B$132,1,MAX(0,1-(E64-$B$132)/(1-$B$132)))</f>
-        <v/>
-      </c>
-      <c r="I64" s="28">
-        <f>IF(C64&gt;=$B$133,MAX($B$134,MIN(F64,G64)*H64),MIN(F64,G64)*H64)</f>
-        <v/>
-      </c>
-      <c r="J64" s="29">
-        <f>REPT("|",ROUND(I64/4,0))</f>
-        <v/>
-      </c>
-      <c r="K64" s="30">
-        <f>VLOOKUP(I64,$A$52:$B$56,2,TRUE)</f>
-        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Six payments in. Confirmed — and Silver, permanently.</t>
+          <t>Opens an account, first payment clears.</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E65" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="26">
-        <f>IF(C65&lt;=$B$129,C65*50/$B$129,IF(C65&gt;=$B$130,100,50+(C65-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C65&lt;=$B$130,C65*50/$B$130,IF(C65&gt;=$B$131,100,50+(C65-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G65" s="26">
-        <f>MIN(D65,$B$131)*100/$B$131</f>
+        <f>MIN(D65,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H65" s="27">
-        <f>IF(E65&lt;=$B$132,1,MAX(0,1-(E65-$B$132)/(1-$B$132)))</f>
+        <f>IF(E65&lt;=$B$133,1,MAX(0,1-(E65-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I65" s="28">
-        <f>IF(C65&gt;=$B$133,MAX($B$134,MIN(F65,G65)*H65),MIN(F65,G65)*H65)</f>
+        <f>IF(C65&gt;=$B$134,MAX($B$135,MIN(F65,G65)*H65),MIN(F65,G65)*H65)</f>
         <v/>
       </c>
       <c r="J65" s="29">
@@ -1582,37 +1544,37 @@
     <row r="66">
       <c r="A66" s="25" t="inlineStr">
         <is>
-          <t>Month 12</t>
+          <t>Month 6</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>One clean year. Gold: credit, card and Rewards all switch on.</t>
+          <t>Six payments in. Confirmed — and Silver, permanently.</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="26">
-        <f>IF(C66&lt;=$B$129,C66*50/$B$129,IF(C66&gt;=$B$130,100,50+(C66-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C66&lt;=$B$130,C66*50/$B$130,IF(C66&gt;=$B$131,100,50+(C66-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>MIN(D66,$B$131)*100/$B$131</f>
+        <f>MIN(D66,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H66" s="27">
-        <f>IF(E66&lt;=$B$132,1,MAX(0,1-(E66-$B$132)/(1-$B$132)))</f>
+        <f>IF(E66&lt;=$B$133,1,MAX(0,1-(E66-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I66" s="28">
-        <f>IF(C66&gt;=$B$133,MAX($B$134,MIN(F66,G66)*H66),MIN(F66,G66)*H66)</f>
+        <f>IF(C66&gt;=$B$134,MAX($B$135,MIN(F66,G66)*H66),MIN(F66,G66)*H66)</f>
         <v/>
       </c>
       <c r="J66" s="29">
@@ -1627,16 +1589,16 @@
     <row r="67">
       <c r="A67" s="25" t="inlineStr">
         <is>
-          <t>Month 24</t>
+          <t>Month 12</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Still paying. Score climbing, tier unchanged.</t>
+          <t>One clean year. Gold: credit, card and Rewards all switch on.</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -1645,19 +1607,19 @@
         <v>0</v>
       </c>
       <c r="F67" s="26">
-        <f>IF(C67&lt;=$B$129,C67*50/$B$129,IF(C67&gt;=$B$130,100,50+(C67-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C67&lt;=$B$130,C67*50/$B$130,IF(C67&gt;=$B$131,100,50+(C67-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G67" s="26">
-        <f>MIN(D67,$B$131)*100/$B$131</f>
+        <f>MIN(D67,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H67" s="27">
-        <f>IF(E67&lt;=$B$132,1,MAX(0,1-(E67-$B$132)/(1-$B$132)))</f>
+        <f>IF(E67&lt;=$B$133,1,MAX(0,1-(E67-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I67" s="28">
-        <f>IF(C67&gt;=$B$133,MAX($B$134,MIN(F67,G67)*H67),MIN(F67,G67)*H67)</f>
+        <f>IF(C67&gt;=$B$134,MAX($B$135,MIN(F67,G67)*H67),MIN(F67,G67)*H67)</f>
         <v/>
       </c>
       <c r="J67" s="29">
@@ -1672,37 +1634,37 @@
     <row r="68">
       <c r="A68" s="25" t="inlineStr">
         <is>
-          <t>Month 30</t>
+          <t>Month 24</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Misses a payment — hospital bill. Costs him nothing today.</t>
+          <t>Still paying. Score climbing, tier unchanged.</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="26">
-        <f>IF(C68&lt;=$B$129,C68*50/$B$129,IF(C68&gt;=$B$130,100,50+(C68-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C68&lt;=$B$130,C68*50/$B$130,IF(C68&gt;=$B$131,100,50+(C68-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G68" s="26">
-        <f>MIN(D68,$B$131)*100/$B$131</f>
+        <f>MIN(D68,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H68" s="27">
-        <f>IF(E68&lt;=$B$132,1,MAX(0,1-(E68-$B$132)/(1-$B$132)))</f>
+        <f>IF(E68&lt;=$B$133,1,MAX(0,1-(E68-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I68" s="28">
-        <f>IF(C68&gt;=$B$133,MAX($B$134,MIN(F68,G68)*H68),MIN(F68,G68)*H68)</f>
+        <f>IF(C68&gt;=$B$134,MAX($B$135,MIN(F68,G68)*H68),MIN(F68,G68)*H68)</f>
         <v/>
       </c>
       <c r="J68" s="29">
@@ -1717,37 +1679,37 @@
     <row r="69">
       <c r="A69" s="25" t="inlineStr">
         <is>
-          <t>Month 36</t>
+          <t>Month 30</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Three calendar years, but 35 payments. Just short of Platinum.</t>
+          <t>Misses a payment — hospital bill. Costs him nothing today.</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="26">
-        <f>IF(C69&lt;=$B$129,C69*50/$B$129,IF(C69&gt;=$B$130,100,50+(C69-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C69&lt;=$B$130,C69*50/$B$130,IF(C69&gt;=$B$131,100,50+(C69-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G69" s="26">
-        <f>MIN(D69,$B$131)*100/$B$131</f>
+        <f>MIN(D69,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H69" s="27">
-        <f>IF(E69&lt;=$B$132,1,MAX(0,1-(E69-$B$132)/(1-$B$132)))</f>
+        <f>IF(E69&lt;=$B$133,1,MAX(0,1-(E69-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I69" s="28">
-        <f>IF(C69&gt;=$B$133,MAX($B$134,MIN(F69,G69)*H69),MIN(F69,G69)*H69)</f>
+        <f>IF(C69&gt;=$B$134,MAX($B$135,MIN(F69,G69)*H69),MIN(F69,G69)*H69)</f>
         <v/>
       </c>
       <c r="J69" s="29">
@@ -1762,16 +1724,16 @@
     <row r="70">
       <c r="A70" s="25" t="inlineStr">
         <is>
-          <t>Month 37</t>
+          <t>Month 36</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>The 36th payment lands. Platinum.</t>
+          <t>Three calendar years, but 35 payments. Just short of Platinum.</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -1780,19 +1742,19 @@
         <v>0</v>
       </c>
       <c r="F70" s="26">
-        <f>IF(C70&lt;=$B$129,C70*50/$B$129,IF(C70&gt;=$B$130,100,50+(C70-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C70&lt;=$B$130,C70*50/$B$130,IF(C70&gt;=$B$131,100,50+(C70-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G70" s="26">
-        <f>MIN(D70,$B$131)*100/$B$131</f>
+        <f>MIN(D70,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H70" s="27">
-        <f>IF(E70&lt;=$B$132,1,MAX(0,1-(E70-$B$132)/(1-$B$132)))</f>
+        <f>IF(E70&lt;=$B$133,1,MAX(0,1-(E70-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I70" s="28">
-        <f>IF(C70&gt;=$B$133,MAX($B$134,MIN(F70,G70)*H70),MIN(F70,G70)*H70)</f>
+        <f>IF(C70&gt;=$B$134,MAX($B$135,MIN(F70,G70)*H70),MIN(F70,G70)*H70)</f>
         <v/>
       </c>
       <c r="J70" s="29">
@@ -1807,37 +1769,37 @@
     <row r="71">
       <c r="A71" s="25" t="inlineStr">
         <is>
-          <t>Month 50</t>
+          <t>Month 37</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Sells a quarter of his gold for a family wedding.</t>
+          <t>The 36th payment lands. Platinum.</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F71" s="26">
-        <f>IF(C71&lt;=$B$129,C71*50/$B$129,IF(C71&gt;=$B$130,100,50+(C71-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C71&lt;=$B$130,C71*50/$B$130,IF(C71&gt;=$B$131,100,50+(C71-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G71" s="26">
-        <f>MIN(D71,$B$131)*100/$B$131</f>
+        <f>MIN(D71,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H71" s="27">
-        <f>IF(E71&lt;=$B$132,1,MAX(0,1-(E71-$B$132)/(1-$B$132)))</f>
+        <f>IF(E71&lt;=$B$133,1,MAX(0,1-(E71-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I71" s="28">
-        <f>IF(C71&gt;=$B$133,MAX($B$134,MIN(F71,G71)*H71),MIN(F71,G71)*H71)</f>
+        <f>IF(C71&gt;=$B$134,MAX($B$135,MIN(F71,G71)*H71),MIN(F71,G71)*H71)</f>
         <v/>
       </c>
       <c r="J71" s="29">
@@ -1852,16 +1814,16 @@
     <row r="72">
       <c r="A72" s="25" t="inlineStr">
         <is>
-          <t>Month 51</t>
+          <t>Month 50</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Inside the allowance. Nothing happened to his score.</t>
+          <t>Sells a quarter of his gold for a family wedding.</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -1870,19 +1832,19 @@
         <v>0.25</v>
       </c>
       <c r="F72" s="26">
-        <f>IF(C72&lt;=$B$129,C72*50/$B$129,IF(C72&gt;=$B$130,100,50+(C72-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C72&lt;=$B$130,C72*50/$B$130,IF(C72&gt;=$B$131,100,50+(C72-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G72" s="26">
-        <f>MIN(D72,$B$131)*100/$B$131</f>
+        <f>MIN(D72,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H72" s="27">
-        <f>IF(E72&lt;=$B$132,1,MAX(0,1-(E72-$B$132)/(1-$B$132)))</f>
+        <f>IF(E72&lt;=$B$133,1,MAX(0,1-(E72-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I72" s="28">
-        <f>IF(C72&gt;=$B$133,MAX($B$134,MIN(F72,G72)*H72),MIN(F72,G72)*H72)</f>
+        <f>IF(C72&gt;=$B$134,MAX($B$135,MIN(F72,G72)*H72),MIN(F72,G72)*H72)</f>
         <v/>
       </c>
       <c r="J72" s="29">
@@ -1897,16 +1859,16 @@
     <row r="73">
       <c r="A73" s="25" t="inlineStr">
         <is>
-          <t>Month 60</t>
+          <t>Month 51</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Five calendar years — but that one miss is still owed.</t>
+          <t>Inside the allowance. Nothing happened to his score.</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -1915,19 +1877,19 @@
         <v>0.25</v>
       </c>
       <c r="F73" s="26">
-        <f>IF(C73&lt;=$B$129,C73*50/$B$129,IF(C73&gt;=$B$130,100,50+(C73-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C73&lt;=$B$130,C73*50/$B$130,IF(C73&gt;=$B$131,100,50+(C73-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G73" s="26">
-        <f>MIN(D73,$B$131)*100/$B$131</f>
+        <f>MIN(D73,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H73" s="27">
-        <f>IF(E73&lt;=$B$132,1,MAX(0,1-(E73-$B$132)/(1-$B$132)))</f>
+        <f>IF(E73&lt;=$B$133,1,MAX(0,1-(E73-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I73" s="28">
-        <f>IF(C73&gt;=$B$133,MAX($B$134,MIN(F73,G73)*H73),MIN(F73,G73)*H73)</f>
+        <f>IF(C73&gt;=$B$134,MAX($B$135,MIN(F73,G73)*H73),MIN(F73,G73)*H73)</f>
         <v/>
       </c>
       <c r="J73" s="29">
@@ -1942,16 +1904,16 @@
     <row r="74">
       <c r="A74" s="25" t="inlineStr">
         <is>
-          <t>Month 61</t>
+          <t>Month 60</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>The 60th payment. Sovereign.</t>
+          <t>Five calendar years — but that one miss is still owed.</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -1960,19 +1922,19 @@
         <v>0.25</v>
       </c>
       <c r="F74" s="26">
-        <f>IF(C74&lt;=$B$129,C74*50/$B$129,IF(C74&gt;=$B$130,100,50+(C74-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(C74&lt;=$B$130,C74*50/$B$130,IF(C74&gt;=$B$131,100,50+(C74-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="G74" s="26">
-        <f>MIN(D74,$B$131)*100/$B$131</f>
+        <f>MIN(D74,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="H74" s="27">
-        <f>IF(E74&lt;=$B$132,1,MAX(0,1-(E74-$B$132)/(1-$B$132)))</f>
+        <f>IF(E74&lt;=$B$133,1,MAX(0,1-(E74-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="I74" s="28">
-        <f>IF(C74&gt;=$B$133,MAX($B$134,MIN(F74,G74)*H74),MIN(F74,G74)*H74)</f>
+        <f>IF(C74&gt;=$B$134,MAX($B$135,MIN(F74,G74)*H74),MIN(F74,G74)*H74)</f>
         <v/>
       </c>
       <c r="J74" s="29">
@@ -1984,462 +1946,466 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>Month 61</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>The 60th payment. Sovereign.</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F75" s="26">
+        <f>IF(C75&lt;=$B$130,C75*50/$B$130,IF(C75&gt;=$B$131,100,50+(C75-$B$130)*50/($B$131-$B$130)))</f>
+        <v/>
+      </c>
+      <c r="G75" s="26">
+        <f>MIN(D75,$B$132)*100/$B$132</f>
+        <v/>
+      </c>
+      <c r="H75" s="27">
+        <f>IF(E75&lt;=$B$133,1,MAX(0,1-(E75-$B$133)/(1-$B$133)))</f>
+        <v/>
+      </c>
+      <c r="I75" s="28">
+        <f>IF(C75&gt;=$B$134,MAX($B$135,MIN(F75,G75)*H75),MIN(F75,G75)*H75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="29">
+        <f>REPT("|",ROUND(I75/4,0))</f>
+        <v/>
+      </c>
+      <c r="K75" s="30">
+        <f>VLOOKUP(I75,$A$52:$B$56,2,TRUE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>The two moments worth pausing on:</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>•   Month 30 — he misses one payment and his tier does not move. The score has slack in the middle of a climb, by design.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>•   Month 50 — he sells a quarter of his gold and nothing happens at all. That is what the one-third allowance is for.</t>
+          <t>•   Month 30 — he misses one payment and his tier does not move. The score has slack in the middle of a climb, by design.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>•   Month 50 — he sells a quarter of his gold and nothing happens at all. That is what the one-third allowance is for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
           <t>•   The whole cost of that one missed payment is that Sovereign arrives in month 61 instead of month 60. One month, and nothing else.</t>
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81"/>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="82"/>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  TRY IT   —   change the blue cells</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-      <c r="K82" s="5" t="n"/>
-      <c r="L82" s="5" t="n"/>
-      <c r="M82" s="5" t="n"/>
-      <c r="N82" s="5" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Enter a customer's position and the model gives you their tier.</t>
         </is>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="20" t="inlineStr">
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="20" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="B86" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C85" s="21" t="inlineStr">
+      <c r="C86" s="21" t="inlineStr">
         <is>
           <t>What it means</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>Months paid — total, lifetime</t>
-        </is>
-      </c>
-      <c r="B86" s="32" t="n">
-        <v>42</v>
-      </c>
-      <c r="C86" s="24" t="inlineStr">
-        <is>
-          <t>Every month a payment cleared. Never falls.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>Months paid — of the last 12</t>
+          <t>Months paid — total, lifetime</t>
         </is>
       </c>
       <c r="B87" s="32" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C87" s="24" t="inlineStr">
         <is>
-          <t>Between 0 and 12.</t>
+          <t>Every month a payment cleared. Never falls.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>Gold held 12 months ago (g)</t>
-        </is>
-      </c>
-      <c r="B88" s="33" t="n">
-        <v>30</v>
+          <t>Months paid — of the last 12</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="n">
+        <v>6</v>
       </c>
       <c r="C88" s="24" t="inlineStr">
         <is>
-          <t>From the token ledger.</t>
+          <t>Between 0 and 12.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>Gold bought since (g)</t>
+          <t>Gold held 12 months ago (g)</t>
         </is>
       </c>
       <c r="B89" s="33" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C89" s="24" t="inlineStr">
         <is>
-          <t>Contributions plus any spot purchases, plus Gold Rewards credited.</t>
+          <t>From the token ledger.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
+          <t>Gold bought since (g)</t>
+        </is>
+      </c>
+      <c r="B90" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>Contributions plus any spot purchases, plus Gold Rewards credited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
           <t>Gold held now (g)</t>
         </is>
       </c>
-      <c r="B90" s="33" t="n">
+      <c r="B91" s="33" t="n">
         <v>38</v>
       </c>
-      <c r="C90" s="24" t="inlineStr">
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>If this equals the two above added together, nothing was sold.</t>
         </is>
       </c>
     </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="20" t="inlineStr">
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>Working</t>
         </is>
       </c>
-      <c r="B92" s="21" t="inlineStr">
+      <c r="B93" s="21" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C92" s="21" t="inlineStr">
+      <c r="C93" s="21" t="inlineStr">
         <is>
           <t>Where it comes from</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Share of your gold sold</t>
         </is>
       </c>
-      <c r="B93" s="34">
-        <f>IF((B88+B89)&lt;=0,0,MAX(0,1-B90/(B88+B89)))</f>
-        <v/>
-      </c>
-      <c r="C93" s="24" t="inlineStr">
+      <c r="B94" s="34">
+        <f>IF((B89+B90)&lt;=0,0,MAX(0,1-B91/(B89+B90)))</f>
+        <v/>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
         <is>
           <t>1 − (held now ÷ [held a year ago + bought since]).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="25" t="inlineStr">
-        <is>
-          <t>RECORD</t>
-        </is>
-      </c>
-      <c r="B94" s="35">
-        <f>IF(B86&lt;=$B$129,B86*50/$B$129,IF(B86&gt;=$B$130,100,50+(B86-$B$129)*50/($B$130-$B$129)))</f>
-        <v/>
-      </c>
-      <c r="C94" s="24" t="inlineStr">
-        <is>
-          <t>Question 1. Months paid, on the strip above.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="25" t="inlineStr">
         <is>
-          <t>STANDING</t>
+          <t>RECORD</t>
         </is>
       </c>
       <c r="B95" s="35">
-        <f>MIN(B87,$B$131)*100/$B$131</f>
+        <f>IF(B87&lt;=$B$130,B87*50/$B$130,IF(B87&gt;=$B$131,100,50+(B87-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>Question 2. Months paid of the last 12.</t>
+          <t>Question 1. Months paid, on the strip above.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="25" t="inlineStr">
         <is>
+          <t>STANDING</t>
+        </is>
+      </c>
+      <c r="B96" s="35">
+        <f>MIN(B88,$B$132)*100/$B$132</f>
+        <v/>
+      </c>
+      <c r="C96" s="24" t="inlineStr">
+        <is>
+          <t>Question 2. Months paid of the last 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="25" t="inlineStr">
+        <is>
           <t>RETENTION</t>
         </is>
       </c>
-      <c r="B96" s="36">
-        <f>IF(B93&lt;=$B$132,1,MAX(0,1-(B93-$B$132)/(1-$B$132)))</f>
-        <v/>
-      </c>
-      <c r="C96" s="24" t="inlineStr">
+      <c r="B97" s="36">
+        <f>IF(B94&lt;=$B$133,1,MAX(0,1-(B94-$B$133)/(1-$B$133)))</f>
+        <v/>
+      </c>
+      <c r="C97" s="24" t="inlineStr">
         <is>
           <t>Question 3. 1.00 means nothing was lost.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>The lower of Record and Standing</t>
         </is>
       </c>
-      <c r="B97" s="35">
-        <f>MIN(B94,B95)</f>
-        <v/>
-      </c>
-      <c r="C97" s="24" t="inlineStr">
+      <c r="B98" s="35">
+        <f>MIN(B95,B96)</f>
+        <v/>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
         <is>
           <t>Both have to be true, so we take the weaker.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="25" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="25" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
-      <c r="B98" s="35">
-        <f>IF(B86&gt;=$B$133,MAX($B$134,B97*B96),B97*B96)</f>
-        <v/>
-      </c>
-      <c r="C98" s="24" t="inlineStr">
+      <c r="B99" s="35">
+        <f>IF(B87&gt;=$B$134,MAX($B$135,B98*B97),B98*B97)</f>
+        <v/>
+      </c>
+      <c r="C99" s="24" t="inlineStr">
         <is>
           <t>Multiplied by Retention, then the floor of 25 if six payments have been made.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="37" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>TIER</t>
         </is>
       </c>
-      <c r="B99" s="38">
-        <f>VLOOKUP(B98,$A$52:$B$56,2,TRUE)</f>
-        <v/>
-      </c>
-      <c r="C99" s="24" t="inlineStr">
+      <c r="B100" s="38">
+        <f>VLOOKUP(B99,$A$52:$B$56,2,TRUE)</f>
+        <v/>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
         <is>
           <t>The highest tier this score has reached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>What is holding them back</t>
-        </is>
-      </c>
-      <c r="B100" s="39">
-        <f>IF(B96&lt;1,"Selling",IF(B94&lt;B95,"Time — keep paying","Discipline — recent misses"))</f>
-        <v/>
-      </c>
-      <c r="C100" s="24" t="inlineStr">
-        <is>
-          <t>The app can tell the customer exactly what to fix. This is the retention hook.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
+          <t>What is holding them back</t>
+        </is>
+      </c>
+      <c r="B101" s="39">
+        <f>IF(B97&lt;1,"Selling",IF(B95&lt;B96,"Time — keep paying","Discipline — recent misses"))</f>
+        <v/>
+      </c>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>The app can tell the customer exactly what to fix. This is the retention hook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
           <t>Six payments made? (drives the floor)</t>
         </is>
       </c>
-      <c r="B101" s="40">
-        <f>IF(B86&gt;=$B$133,"Yes — Silver secured","Not yet")</f>
-        <v/>
-      </c>
-      <c r="C101" s="24" t="inlineStr">
+      <c r="B102" s="40">
+        <f>IF(B87&gt;=$B$134,"Yes — Silver secured","Not yet")</f>
+        <v/>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
         <is>
           <t>Confirmed status is simply the 6th payment. It is permanent.</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
     <row r="103"/>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="104"/>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  EVERY CASE THAT MATTERS</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n"/>
-      <c r="M104" s="5" t="n"/>
-      <c r="N104" s="5" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+      <c r="B105" s="5" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>The rows we would expect a sharp reader to test. All of them are live.</t>
         </is>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="A107" s="20" t="inlineStr">
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>Months</t>
         </is>
       </c>
-      <c r="C107" s="21" t="inlineStr">
+      <c r="C108" s="21" t="inlineStr">
         <is>
           <t>of last 12</t>
         </is>
       </c>
-      <c r="D107" s="21" t="inlineStr">
+      <c r="D108" s="21" t="inlineStr">
         <is>
           <t>Sold</t>
         </is>
       </c>
-      <c r="E107" s="21" t="inlineStr">
+      <c r="E108" s="21" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="F107" s="21" t="inlineStr">
+      <c r="F108" s="21" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="G107" s="21" t="inlineStr">
+      <c r="G108" s="21" t="inlineStr">
         <is>
           <t>Retention</t>
         </is>
       </c>
-      <c r="H107" s="21" t="inlineStr">
+      <c r="H108" s="21" t="inlineStr">
         <is>
           <t>SCORE</t>
         </is>
       </c>
-      <c r="I107" s="21" t="inlineStr">
+      <c r="I108" s="21" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="J107" s="21" t="inlineStr">
+      <c r="J108" s="21" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="41" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="41" t="inlineStr">
         <is>
           <t>FAIRNESS</t>
         </is>
       </c>
-      <c r="B108" s="42" t="n"/>
-      <c r="C108" s="42" t="n"/>
-      <c r="D108" s="42" t="n"/>
-      <c r="E108" s="42" t="n"/>
-      <c r="F108" s="42" t="n"/>
-      <c r="G108" s="42" t="n"/>
-      <c r="H108" s="42" t="n"/>
-      <c r="I108" s="42" t="n"/>
-      <c r="J108" s="42" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   USD 20 a month, perfect, five years</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="C109" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D109" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="26">
-        <f>IF(B109&lt;=$B$129,B109*50/$B$129,IF(B109&gt;=$B$130,100,50+(B109-$B$129)*50/($B$130-$B$129)))</f>
-        <v/>
-      </c>
-      <c r="F109" s="26">
-        <f>MIN(C109,$B$131)*100/$B$131</f>
-        <v/>
-      </c>
-      <c r="G109" s="27">
-        <f>IF(D109&lt;=$B$132,1,MAX(0,1-(D109-$B$132)/(1-$B$132)))</f>
-        <v/>
-      </c>
-      <c r="H109" s="43">
-        <f>IF(B109&gt;=$B$133,MAX($B$134,MIN(E109,F109)*G109),MIN(E109,F109)*G109)</f>
-        <v/>
-      </c>
-      <c r="I109" s="30">
-        <f>VLOOKUP(H109,$A$52:$B$56,2,TRUE)</f>
-        <v/>
-      </c>
-      <c r="J109" s="24" t="inlineStr">
-        <is>
-          <t>The smallest saver in the product reaches the top. This is the test the design exists to pass.</t>
-        </is>
-      </c>
+      <c r="B109" s="42" t="n"/>
+      <c r="C109" s="42" t="n"/>
+      <c r="D109" s="42" t="n"/>
+      <c r="E109" s="42" t="n"/>
+      <c r="F109" s="42" t="n"/>
+      <c r="G109" s="42" t="n"/>
+      <c r="H109" s="42" t="n"/>
+      <c r="I109" s="42" t="n"/>
+      <c r="J109" s="42" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   USD 2,000 a month, perfect, five years</t>
+          <t xml:space="preserve">   USD 20 a month, perfect, five years</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -2452,19 +2418,19 @@
         <v>0</v>
       </c>
       <c r="E110" s="26">
-        <f>IF(B110&lt;=$B$129,B110*50/$B$129,IF(B110&gt;=$B$130,100,50+(B110-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B110&lt;=$B$130,B110*50/$B$130,IF(B110&gt;=$B$131,100,50+(B110-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F110" s="26">
-        <f>MIN(C110,$B$131)*100/$B$131</f>
+        <f>MIN(C110,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G110" s="27">
-        <f>IF(D110&lt;=$B$132,1,MAX(0,1-(D110-$B$132)/(1-$B$132)))</f>
+        <f>IF(D110&lt;=$B$133,1,MAX(0,1-(D110-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H110" s="43">
-        <f>IF(B110&gt;=$B$133,MAX($B$134,MIN(E110,F110)*G110),MIN(E110,F110)*G110)</f>
+        <f>IF(B110&gt;=$B$134,MAX($B$135,MIN(E110,F110)*G110),MIN(E110,F110)*G110)</f>
         <v/>
       </c>
       <c r="I110" s="30">
@@ -2473,39 +2439,39 @@
       </c>
       <c r="J110" s="24" t="inlineStr">
         <is>
-          <t>Identical, to the day. A hundred times the money buys zero tiers.</t>
+          <t>The smallest saver in the product reaches the top. This is the test the design exists to pass.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Six payments scattered over three years</t>
+          <t xml:space="preserve">   USD 2,000 a month, perfect, five years</t>
         </is>
       </c>
       <c r="B111" s="11" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D111" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="26">
-        <f>IF(B111&lt;=$B$129,B111*50/$B$129,IF(B111&gt;=$B$130,100,50+(B111-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B111&lt;=$B$130,B111*50/$B$130,IF(B111&gt;=$B$131,100,50+(B111-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F111" s="26">
-        <f>MIN(C111,$B$131)*100/$B$131</f>
+        <f>MIN(C111,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G111" s="27">
-        <f>IF(D111&lt;=$B$132,1,MAX(0,1-(D111-$B$132)/(1-$B$132)))</f>
+        <f>IF(D111&lt;=$B$133,1,MAX(0,1-(D111-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H111" s="43">
-        <f>IF(B111&gt;=$B$133,MAX($B$134,MIN(E111,F111)*G111),MIN(E111,F111)*G111)</f>
+        <f>IF(B111&gt;=$B$134,MAX($B$135,MIN(E111,F111)*G111),MIN(E111,F111)*G111)</f>
         <v/>
       </c>
       <c r="I111" s="30">
@@ -2514,71 +2480,71 @@
       </c>
       <c r="J111" s="24" t="inlineStr">
         <is>
-          <t>Earns Silver and stops. The floor holds him; nothing above it is reachable without current form.</t>
+          <t>Identical, to the day. A hundred times the money buys zero tiers.</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="41" t="inlineStr">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Six payments scattered, never six in a row</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="26">
+        <f>IF(B112&lt;=$B$130,B112*50/$B$130,IF(B112&gt;=$B$131,100,50+(B112-$B$130)*50/($B$131-$B$130)))</f>
+        <v/>
+      </c>
+      <c r="F112" s="26">
+        <f>MIN(C112,$B$132)*100/$B$132</f>
+        <v/>
+      </c>
+      <c r="G112" s="27">
+        <f>IF(D112&lt;=$B$133,1,MAX(0,1-(D112-$B$133)/(1-$B$133)))</f>
+        <v/>
+      </c>
+      <c r="H112" s="43">
+        <f>IF(B112&gt;=$B$134,MAX($B$135,MIN(E112,F112)*G112),MIN(E112,F112)*G112)</f>
+        <v/>
+      </c>
+      <c r="I112" s="30">
+        <f>VLOOKUP(H112,$A$52:$B$56,2,TRUE)</f>
+        <v/>
+      </c>
+      <c r="J112" s="24" t="inlineStr">
+        <is>
+          <t>Never passes the gate, so no score is ever calculated. Six real payments, no tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="41" t="inlineStr">
         <is>
           <t>SELLING</t>
         </is>
       </c>
-      <c r="B112" s="42" t="n"/>
-      <c r="C112" s="42" t="n"/>
-      <c r="D112" s="42" t="n"/>
-      <c r="E112" s="42" t="n"/>
-      <c r="F112" s="42" t="n"/>
-      <c r="G112" s="42" t="n"/>
-      <c r="H112" s="42" t="n"/>
-      <c r="I112" s="42" t="n"/>
-      <c r="J112" s="42" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Sells a quarter of his gold</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="C113" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D113" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E113" s="26">
-        <f>IF(B113&lt;=$B$129,B113*50/$B$129,IF(B113&gt;=$B$130,100,50+(B113-$B$129)*50/($B$130-$B$129)))</f>
-        <v/>
-      </c>
-      <c r="F113" s="26">
-        <f>MIN(C113,$B$131)*100/$B$131</f>
-        <v/>
-      </c>
-      <c r="G113" s="27">
-        <f>IF(D113&lt;=$B$132,1,MAX(0,1-(D113-$B$132)/(1-$B$132)))</f>
-        <v/>
-      </c>
-      <c r="H113" s="43">
-        <f>IF(B113&gt;=$B$133,MAX($B$134,MIN(E113,F113)*G113),MIN(E113,F113)*G113)</f>
-        <v/>
-      </c>
-      <c r="I113" s="30">
-        <f>VLOOKUP(H113,$A$52:$B$56,2,TRUE)</f>
-        <v/>
-      </c>
-      <c r="J113" s="24" t="inlineStr">
-        <is>
-          <t>Inside the allowance. Nothing happens.</t>
-        </is>
-      </c>
+      <c r="B113" s="42" t="n"/>
+      <c r="C113" s="42" t="n"/>
+      <c r="D113" s="42" t="n"/>
+      <c r="E113" s="42" t="n"/>
+      <c r="F113" s="42" t="n"/>
+      <c r="G113" s="42" t="n"/>
+      <c r="H113" s="42" t="n"/>
+      <c r="I113" s="42" t="n"/>
+      <c r="J113" s="42" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Sells a third</t>
+          <t xml:space="preserve">   Sells a quarter of his gold</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
@@ -2588,22 +2554,22 @@
         <v>12</v>
       </c>
       <c r="D114" s="15" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E114" s="26">
-        <f>IF(B114&lt;=$B$129,B114*50/$B$129,IF(B114&gt;=$B$130,100,50+(B114-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B114&lt;=$B$130,B114*50/$B$130,IF(B114&gt;=$B$131,100,50+(B114-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F114" s="26">
-        <f>MIN(C114,$B$131)*100/$B$131</f>
+        <f>MIN(C114,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G114" s="27">
-        <f>IF(D114&lt;=$B$132,1,MAX(0,1-(D114-$B$132)/(1-$B$132)))</f>
+        <f>IF(D114&lt;=$B$133,1,MAX(0,1-(D114-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H114" s="43">
-        <f>IF(B114&gt;=$B$133,MAX($B$134,MIN(E114,F114)*G114),MIN(E114,F114)*G114)</f>
+        <f>IF(B114&gt;=$B$134,MAX($B$135,MIN(E114,F114)*G114),MIN(E114,F114)*G114)</f>
         <v/>
       </c>
       <c r="I114" s="30">
@@ -2612,14 +2578,14 @@
       </c>
       <c r="J114" s="24" t="inlineStr">
         <is>
-          <t>Exactly on the line. Still nothing.</t>
+          <t>Inside the allowance. Nothing happens.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Sells half</t>
+          <t xml:space="preserve">   Sells a third</t>
         </is>
       </c>
       <c r="B115" s="11" t="n">
@@ -2629,22 +2595,22 @@
         <v>12</v>
       </c>
       <c r="D115" s="15" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E115" s="26">
-        <f>IF(B115&lt;=$B$129,B115*50/$B$129,IF(B115&gt;=$B$130,100,50+(B115-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B115&lt;=$B$130,B115*50/$B$130,IF(B115&gt;=$B$131,100,50+(B115-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F115" s="26">
-        <f>MIN(C115,$B$131)*100/$B$131</f>
+        <f>MIN(C115,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G115" s="27">
-        <f>IF(D115&lt;=$B$132,1,MAX(0,1-(D115-$B$132)/(1-$B$132)))</f>
+        <f>IF(D115&lt;=$B$133,1,MAX(0,1-(D115-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H115" s="43">
-        <f>IF(B115&gt;=$B$133,MAX($B$134,MIN(E115,F115)*G115),MIN(E115,F115)*G115)</f>
+        <f>IF(B115&gt;=$B$134,MAX($B$135,MIN(E115,F115)*G115),MIN(E115,F115)*G115)</f>
         <v/>
       </c>
       <c r="I115" s="30">
@@ -2653,14 +2619,14 @@
       </c>
       <c r="J115" s="24" t="inlineStr">
         <is>
-          <t>One tier. He keeps his gold, his loan and his card.</t>
+          <t>Exactly on the line. Still nothing.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Sells everything</t>
+          <t xml:space="preserve">   Sells half</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
@@ -2670,22 +2636,22 @@
         <v>12</v>
       </c>
       <c r="D116" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E116" s="26">
-        <f>IF(B116&lt;=$B$129,B116*50/$B$129,IF(B116&gt;=$B$130,100,50+(B116-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B116&lt;=$B$130,B116*50/$B$130,IF(B116&gt;=$B$131,100,50+(B116-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F116" s="26">
-        <f>MIN(C116,$B$131)*100/$B$131</f>
+        <f>MIN(C116,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G116" s="27">
-        <f>IF(D116&lt;=$B$132,1,MAX(0,1-(D116-$B$132)/(1-$B$132)))</f>
+        <f>IF(D116&lt;=$B$133,1,MAX(0,1-(D116-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H116" s="43">
-        <f>IF(B116&gt;=$B$133,MAX($B$134,MIN(E116,F116)*G116),MIN(E116,F116)*G116)</f>
+        <f>IF(B116&gt;=$B$134,MAX($B$135,MIN(E116,F116)*G116),MIN(E116,F116)*G116)</f>
         <v/>
       </c>
       <c r="I116" s="30">
@@ -2694,18 +2660,18 @@
       </c>
       <c r="J116" s="24" t="inlineStr">
         <is>
-          <t>Three tiers, to the floor. Recovers in twelve clean months.</t>
+          <t>One tier. He keeps his gold, his loan and his card.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The cycler — buys and sells every month</t>
+          <t xml:space="preserve">   Sells everything</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C117" s="11" t="n">
         <v>12</v>
@@ -2714,19 +2680,19 @@
         <v>1</v>
       </c>
       <c r="E117" s="26">
-        <f>IF(B117&lt;=$B$129,B117*50/$B$129,IF(B117&gt;=$B$130,100,50+(B117-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B117&lt;=$B$130,B117*50/$B$130,IF(B117&gt;=$B$131,100,50+(B117-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F117" s="26">
-        <f>MIN(C117,$B$131)*100/$B$131</f>
+        <f>MIN(C117,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G117" s="27">
-        <f>IF(D117&lt;=$B$132,1,MAX(0,1-(D117-$B$132)/(1-$B$132)))</f>
+        <f>IF(D117&lt;=$B$133,1,MAX(0,1-(D117-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H117" s="43">
-        <f>IF(B117&gt;=$B$133,MAX($B$134,MIN(E117,F117)*G117),MIN(E117,F117)*G117)</f>
+        <f>IF(B117&gt;=$B$134,MAX($B$135,MIN(E117,F117)*G117),MIN(E117,F117)*G117)</f>
         <v/>
       </c>
       <c r="I117" s="30">
@@ -2735,96 +2701,96 @@
       </c>
       <c r="J117" s="24" t="inlineStr">
         <is>
+          <t>Three tiers, to the floor. Recovers in twelve clean months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The cycler — buys and sells every month</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="26">
+        <f>IF(B118&lt;=$B$130,B118*50/$B$130,IF(B118&gt;=$B$131,100,50+(B118-$B$130)*50/($B$131-$B$130)))</f>
+        <v/>
+      </c>
+      <c r="F118" s="26">
+        <f>MIN(C118,$B$132)*100/$B$132</f>
+        <v/>
+      </c>
+      <c r="G118" s="27">
+        <f>IF(D118&lt;=$B$133,1,MAX(0,1-(D118-$B$133)/(1-$B$133)))</f>
+        <v/>
+      </c>
+      <c r="H118" s="43">
+        <f>IF(B118&gt;=$B$134,MAX($B$135,MIN(E118,F118)*G118),MIN(E118,F118)*G118)</f>
+        <v/>
+      </c>
+      <c r="I118" s="30">
+        <f>VLOOKUP(H118,$A$52:$B$56,2,TRUE)</f>
+        <v/>
+      </c>
+      <c r="J118" s="24" t="inlineStr">
+        <is>
           <t>A flawless payment record held at Silver. He never recovers, because he never stops.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="41" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="41" t="inlineStr">
         <is>
           <t>MISSING PAYMENTS  (a ten-year saver who stops)</t>
         </is>
       </c>
-      <c r="B118" s="42" t="n"/>
-      <c r="C118" s="42" t="n"/>
-      <c r="D118" s="42" t="n"/>
-      <c r="E118" s="42" t="n"/>
-      <c r="F118" s="42" t="n"/>
-      <c r="G118" s="42" t="n"/>
-      <c r="H118" s="42" t="n"/>
-      <c r="I118" s="42" t="n"/>
-      <c r="J118" s="42" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   one missed month</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="C119" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D119" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="26">
-        <f>IF(B119&lt;=$B$129,B119*50/$B$129,IF(B119&gt;=$B$130,100,50+(B119-$B$129)*50/($B$130-$B$129)))</f>
-        <v/>
-      </c>
-      <c r="F119" s="26">
-        <f>MIN(C119,$B$131)*100/$B$131</f>
-        <v/>
-      </c>
-      <c r="G119" s="27">
-        <f>IF(D119&lt;=$B$132,1,MAX(0,1-(D119-$B$132)/(1-$B$132)))</f>
-        <v/>
-      </c>
-      <c r="H119" s="43">
-        <f>IF(B119&gt;=$B$133,MAX($B$134,MIN(E119,F119)*G119),MIN(E119,F119)*G119)</f>
-        <v/>
-      </c>
-      <c r="I119" s="30">
-        <f>VLOOKUP(H119,$A$52:$B$56,2,TRUE)</f>
-        <v/>
-      </c>
-      <c r="J119" s="24" t="inlineStr">
-        <is>
-          <t>One tier.</t>
-        </is>
-      </c>
+      <c r="B119" s="42" t="n"/>
+      <c r="C119" s="42" t="n"/>
+      <c r="D119" s="42" t="n"/>
+      <c r="E119" s="42" t="n"/>
+      <c r="F119" s="42" t="n"/>
+      <c r="G119" s="42" t="n"/>
+      <c r="H119" s="42" t="n"/>
+      <c r="I119" s="42" t="n"/>
+      <c r="J119" s="42" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   three missed months</t>
+          <t xml:space="preserve">   one missed month</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
         <v>120</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D120" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="26">
-        <f>IF(B120&lt;=$B$129,B120*50/$B$129,IF(B120&gt;=$B$130,100,50+(B120-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B120&lt;=$B$130,B120*50/$B$130,IF(B120&gt;=$B$131,100,50+(B120-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F120" s="26">
-        <f>MIN(C120,$B$131)*100/$B$131</f>
+        <f>MIN(C120,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G120" s="27">
-        <f>IF(D120&lt;=$B$132,1,MAX(0,1-(D120-$B$132)/(1-$B$132)))</f>
+        <f>IF(D120&lt;=$B$133,1,MAX(0,1-(D120-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H120" s="43">
-        <f>IF(B120&gt;=$B$133,MAX($B$134,MIN(E120,F120)*G120),MIN(E120,F120)*G120)</f>
+        <f>IF(B120&gt;=$B$134,MAX($B$135,MIN(E120,F120)*G120),MIN(E120,F120)*G120)</f>
         <v/>
       </c>
       <c r="I120" s="30">
@@ -2833,39 +2799,39 @@
       </c>
       <c r="J120" s="24" t="inlineStr">
         <is>
-          <t>Still Platinum. It takes four in a row to lose it.</t>
+          <t>One tier.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   four missed months</t>
+          <t xml:space="preserve">   three missed months</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
         <v>120</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D121" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E121" s="26">
-        <f>IF(B121&lt;=$B$129,B121*50/$B$129,IF(B121&gt;=$B$130,100,50+(B121-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B121&lt;=$B$130,B121*50/$B$130,IF(B121&gt;=$B$131,100,50+(B121-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F121" s="26">
-        <f>MIN(C121,$B$131)*100/$B$131</f>
+        <f>MIN(C121,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G121" s="27">
-        <f>IF(D121&lt;=$B$132,1,MAX(0,1-(D121-$B$132)/(1-$B$132)))</f>
+        <f>IF(D121&lt;=$B$133,1,MAX(0,1-(D121-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H121" s="43">
-        <f>IF(B121&gt;=$B$133,MAX($B$134,MIN(E121,F121)*G121),MIN(E121,F121)*G121)</f>
+        <f>IF(B121&gt;=$B$134,MAX($B$135,MIN(E121,F121)*G121),MIN(E121,F121)*G121)</f>
         <v/>
       </c>
       <c r="I121" s="30">
@@ -2874,39 +2840,39 @@
       </c>
       <c r="J121" s="24" t="inlineStr">
         <is>
-          <t>Platinum lost.</t>
+          <t>Still Platinum. It takes four in a row to lose it.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   seven missed months</t>
+          <t xml:space="preserve">   four missed months</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
         <v>120</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E122" s="26">
-        <f>IF(B122&lt;=$B$129,B122*50/$B$129,IF(B122&gt;=$B$130,100,50+(B122-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B122&lt;=$B$130,B122*50/$B$130,IF(B122&gt;=$B$131,100,50+(B122-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F122" s="26">
-        <f>MIN(C122,$B$131)*100/$B$131</f>
+        <f>MIN(C122,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G122" s="27">
-        <f>IF(D122&lt;=$B$132,1,MAX(0,1-(D122-$B$132)/(1-$B$132)))</f>
+        <f>IF(D122&lt;=$B$133,1,MAX(0,1-(D122-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H122" s="43">
-        <f>IF(B122&gt;=$B$133,MAX($B$134,MIN(E122,F122)*G122),MIN(E122,F122)*G122)</f>
+        <f>IF(B122&gt;=$B$134,MAX($B$135,MIN(E122,F122)*G122),MIN(E122,F122)*G122)</f>
         <v/>
       </c>
       <c r="I122" s="30">
@@ -2915,39 +2881,39 @@
       </c>
       <c r="J122" s="24" t="inlineStr">
         <is>
-          <t>Gold lost.</t>
+          <t>Platinum lost.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   stopped for a full year</t>
+          <t xml:space="preserve">   seven missed months</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
         <v>120</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D123" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E123" s="26">
-        <f>IF(B123&lt;=$B$129,B123*50/$B$129,IF(B123&gt;=$B$130,100,50+(B123-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B123&lt;=$B$130,B123*50/$B$130,IF(B123&gt;=$B$131,100,50+(B123-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F123" s="26">
-        <f>MIN(C123,$B$131)*100/$B$131</f>
+        <f>MIN(C123,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G123" s="27">
-        <f>IF(D123&lt;=$B$132,1,MAX(0,1-(D123-$B$132)/(1-$B$132)))</f>
+        <f>IF(D123&lt;=$B$133,1,MAX(0,1-(D123-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H123" s="43">
-        <f>IF(B123&gt;=$B$133,MAX($B$134,MIN(E123,F123)*G123),MIN(E123,F123)*G123)</f>
+        <f>IF(B123&gt;=$B$134,MAX($B$135,MIN(E123,F123)*G123),MIN(E123,F123)*G123)</f>
         <v/>
       </c>
       <c r="I123" s="30">
@@ -2956,39 +2922,39 @@
       </c>
       <c r="J123" s="24" t="inlineStr">
         <is>
-          <t>Ten years of history does not hold the top tier. Status is rented, not owned.</t>
+          <t>Gold lost.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   pays every other month, forever</t>
+          <t xml:space="preserve">   stopped for a full year</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E124" s="26">
-        <f>IF(B124&lt;=$B$129,B124*50/$B$129,IF(B124&gt;=$B$130,100,50+(B124-$B$129)*50/($B$130-$B$129)))</f>
+        <f>IF(B124&lt;=$B$130,B124*50/$B$130,IF(B124&gt;=$B$131,100,50+(B124-$B$130)*50/($B$131-$B$130)))</f>
         <v/>
       </c>
       <c r="F124" s="26">
-        <f>MIN(C124,$B$131)*100/$B$131</f>
+        <f>MIN(C124,$B$132)*100/$B$132</f>
         <v/>
       </c>
       <c r="G124" s="27">
-        <f>IF(D124&lt;=$B$132,1,MAX(0,1-(D124-$B$132)/(1-$B$132)))</f>
+        <f>IF(D124&lt;=$B$133,1,MAX(0,1-(D124-$B$133)/(1-$B$133)))</f>
         <v/>
       </c>
       <c r="H124" s="43">
-        <f>IF(B124&gt;=$B$133,MAX($B$134,MIN(E124,F124)*G124),MIN(E124,F124)*G124)</f>
+        <f>IF(B124&gt;=$B$134,MAX($B$135,MIN(E124,F124)*G124),MIN(E124,F124)*G124)</f>
         <v/>
       </c>
       <c r="I124" s="30">
@@ -2997,142 +2963,183 @@
       </c>
       <c r="J124" s="24" t="inlineStr">
         <is>
+          <t>Ten years of history does not hold the top tier. Status is rented, not owned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   pays every other month, forever</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="26">
+        <f>IF(B125&lt;=$B$130,B125*50/$B$130,IF(B125&gt;=$B$131,100,50+(B125-$B$130)*50/($B$131-$B$130)))</f>
+        <v/>
+      </c>
+      <c r="F125" s="26">
+        <f>MIN(C125,$B$132)*100/$B$132</f>
+        <v/>
+      </c>
+      <c r="G125" s="27">
+        <f>IF(D125&lt;=$B$133,1,MAX(0,1-(D125-$B$133)/(1-$B$133)))</f>
+        <v/>
+      </c>
+      <c r="H125" s="43">
+        <f>IF(B125&gt;=$B$134,MAX($B$135,MIN(E125,F125)*G125),MIN(E125,F125)*G125)</f>
+        <v/>
+      </c>
+      <c r="I125" s="30">
+        <f>VLOOKUP(H125,$A$52:$B$56,2,TRUE)</f>
+        <v/>
+      </c>
+      <c r="J125" s="24" t="inlineStr">
+        <is>
           <t>Capped at Gold for life. Nothing in the rules stops him — the arithmetic does.</t>
         </is>
       </c>
     </row>
-    <row r="125"/>
     <row r="126"/>
-    <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
+    <row r="127"/>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  THE NUMBERS WE CHOSE   —   everything above is driven by these six cells</t>
         </is>
       </c>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="5" t="n"/>
-      <c r="E127" s="5" t="n"/>
-      <c r="F127" s="5" t="n"/>
-      <c r="G127" s="5" t="n"/>
-      <c r="H127" s="5" t="n"/>
-      <c r="I127" s="5" t="n"/>
-      <c r="J127" s="5" t="n"/>
-      <c r="K127" s="5" t="n"/>
-      <c r="L127" s="5" t="n"/>
-      <c r="M127" s="5" t="n"/>
-      <c r="N127" s="5" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="5" t="n"/>
+      <c r="J128" s="5" t="n"/>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B128" s="21" t="inlineStr">
+      <c r="B129" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C128" s="21" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>Why this number</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>Months to reach a Record of 50</t>
-        </is>
-      </c>
-      <c r="B129" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="C129" s="24" t="inlineStr">
-        <is>
-          <t>One year. The first year is the hardest, so it is worth the most.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>Months to reach a Record of 100</t>
+          <t>Months to reach a Record of 50</t>
         </is>
       </c>
       <c r="B130" s="32" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>Five years. Long enough to be meaningful, short enough to be reachable.</t>
+          <t>One year. The first year is the hardest, so it is worth the most.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Trailing window (months)</t>
+          <t>Months to reach a Record of 100</t>
         </is>
       </c>
       <c r="B131" s="32" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>A year. Long enough to see a habit, short enough to forgive an accident.</t>
+          <t>Five years. Long enough to be meaningful, short enough to be reachable.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>Free withdrawal allowance</t>
-        </is>
-      </c>
-      <c r="B132" s="44" t="n">
-        <v>0.3</v>
+          <t>Trailing window (months)</t>
+        </is>
+      </c>
+      <c r="B132" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>A third. Covers a genuine household need without touching the score.</t>
+          <t>A year. Long enough to see a habit, short enough to forgive an accident.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Payments that secure Silver</t>
-        </is>
-      </c>
-      <c r="B133" s="32" t="n">
-        <v>6</v>
+          <t>Free withdrawal allowance</t>
+        </is>
+      </c>
+      <c r="B133" s="44" t="n">
+        <v>0.3</v>
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Six. Proves the account is real. Permanent once earned.</t>
+          <t>A third. Covers a genuine household need without touching the score.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
+          <t>Payments that secure Silver</t>
+        </is>
+      </c>
+      <c r="B134" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C134" s="24" t="inlineStr">
+        <is>
+          <t>Six. Proves the account is real. Permanent once earned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
           <t>Silver floor score</t>
         </is>
       </c>
-      <c r="B134" s="32" t="n">
+      <c r="B135" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="C134" s="24" t="inlineStr">
+      <c r="C135" s="24" t="inlineStr">
         <is>
           <t>Nobody who has made six payments is ever sent back to the beginning.</t>
         </is>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>The one number worth revisiting once we have real data is the withdrawal allowance. Everything else is structural.</t>
         </is>

--- a/deliverables/2-mechanism-design/Aurumix_ICS_Score_Calculator.xlsx
+++ b/deliverables/2-mechanism-design/Aurumix_ICS_Score_Calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://khiibaedu-my.sharepoint.com/personal/a_rehman_16863_khi_iba_edu_pk/Documents/Desktop/Aurumix/deliverables/2-mechanism-design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_8413C6AA944726CF6264C4B54C5DCE3AF7434917" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1D8809-AA7C-4FF1-817F-D54B2D729A40}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_8413C6AA944726CF6264C4B54C5DCE3AF7434917" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD92643-3133-4958-8EEF-6BB240F77262}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="181">
   <si>
     <t>AURUMIX  ·  THE INVESTOR CONVICTION SCORE</t>
   </si>
@@ -215,9 +215,6 @@
     <t>Silver is permanent. Every tier above it is rented by conduct — which is the point.</t>
   </si>
   <si>
-    <t xml:space="preserve">  A WORKED STORY   —   Rajesh, USD 75 a month</t>
-  </si>
-  <si>
     <t>One missed payment and one real withdrawal, across five years. Follow the last two columns.</t>
   </si>
   <si>
@@ -573,6 +570,12 @@
   </si>
   <si>
     <t>The one number worth revisiting once we have real data is the withdrawal allowance. Everything else is structural.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  A WORKED STORY   —   Tony, USD 75 a month</t>
   </si>
 </sst>
 </file>
@@ -873,6 +876,989 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Retention Score</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>ICS!$B$37:$L$37</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ICS!$B$38:$L$38</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8571428571428571</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.71428571428571419</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.5714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.2857142857142857</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14285714285714268</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-111F-4350-9D38-D2602ED7A8C4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1467244095"/>
+        <c:axId val="736243279"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1467244095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="736243279"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="736243279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1467244095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2324100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1F730E-08D9-628D-4C6F-1283C58D64F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1636,6 +2622,11 @@
         <v>32</v>
       </c>
     </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J40" t="s">
+        <v>179</v>
+      </c>
+    </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>33</v>
@@ -1801,7 +2792,7 @@
     </row>
     <row r="61" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -1819,36 +2810,36 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="C64" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="D64" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="E64" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="21" t="s">
+      <c r="F64" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F64" s="21" t="s">
+      <c r="G64" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="G64" s="21" t="s">
+      <c r="H64" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="H64" s="21" t="s">
+      <c r="I64" s="21" t="s">
         <v>69</v>
-      </c>
-      <c r="I64" s="21" t="s">
-        <v>70</v>
       </c>
       <c r="J64" s="21"/>
       <c r="K64" s="21" t="s">
@@ -1857,10 +2848,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="C65" s="11">
         <v>1</v>
@@ -1898,10 +2889,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="C66" s="11">
         <v>6</v>
@@ -1939,10 +2930,10 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="C67" s="11">
         <v>12</v>
@@ -1980,10 +2971,10 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="C68" s="11">
         <v>24</v>
@@ -2021,10 +3012,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="C69" s="11">
         <v>29</v>
@@ -2062,10 +3053,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="C70" s="11">
         <v>35</v>
@@ -2103,10 +3094,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="C71" s="11">
         <v>36</v>
@@ -2144,10 +3135,10 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B72" s="9" t="s">
         <v>85</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="C72" s="11">
         <v>49</v>
@@ -2185,10 +3176,10 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="C73" s="11">
         <v>50</v>
@@ -2226,10 +3217,10 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C74" s="11">
         <v>59</v>
@@ -2267,10 +3258,10 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="C75" s="11">
         <v>60</v>
@@ -2308,27 +3299,27 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2346,96 +3337,96 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="21" t="s">
+      <c r="C86" s="21" t="s">
         <v>100</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B87" s="32">
         <v>42</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B88" s="32">
         <v>6</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B89" s="33">
         <v>30</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" s="33">
         <v>8</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B91" s="33">
         <v>38</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B93" s="21" t="s">
+      <c r="C93" s="21" t="s">
         <v>113</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B94" s="34">
         <f>IF((B89+B90)&lt;=0,0,MAX(0,1-B91/(B89+B90)))</f>
         <v>0</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -2447,7 +3438,7 @@
         <v>81.25</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -2459,7 +3450,7 @@
         <v>50</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -2471,72 +3462,72 @@
         <v>1</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B98" s="35">
         <f>MIN(B95,B96)</f>
         <v>50</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B99" s="35">
         <f>IF(B87&gt;=$B$134,MAX($B$135,B98*B97),B98*B97)</f>
         <v>50</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A100" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B100" s="38" t="str">
         <f>VLOOKUP(B99,$A$52:$B$56,2,TRUE)</f>
         <v>Gold</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B101" s="39" t="str">
         <f>IF(B97&lt;1,"Selling",IF(B95&lt;B96,"Time — keep paying","Discipline — recent misses"))</f>
         <v>Discipline — recent misses</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B102" s="40" t="str">
         <f>IF(B87&gt;=$B$134,"Yes — Silver secured","Not yet")</f>
         <v>Yes — Silver secured</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -2554,44 +3545,44 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B108" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C108" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C108" s="21" t="s">
+      <c r="D108" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D108" s="21" t="s">
+      <c r="E108" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E108" s="21" t="s">
+      <c r="F108" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="F108" s="21" t="s">
+      <c r="G108" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G108" s="21" t="s">
+      <c r="H108" s="21" t="s">
         <v>69</v>
-      </c>
-      <c r="H108" s="21" t="s">
-        <v>70</v>
       </c>
       <c r="I108" s="21" t="s">
         <v>40</v>
       </c>
       <c r="J108" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B109" s="42"/>
       <c r="C109" s="42"/>
@@ -2605,7 +3596,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B110" s="11">
         <v>60</v>
@@ -2637,12 +3628,12 @@
         <v>Sovereign</v>
       </c>
       <c r="J110" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B111" s="11">
         <v>60</v>
@@ -2674,12 +3665,12 @@
         <v>Sovereign</v>
       </c>
       <c r="J111" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B112" s="11">
         <v>0</v>
@@ -2711,12 +3702,12 @@
         <v>No tier</v>
       </c>
       <c r="J112" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B113" s="42"/>
       <c r="C113" s="42"/>
@@ -2730,7 +3721,7 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B114" s="11">
         <v>36</v>
@@ -2762,12 +3753,12 @@
         <v>Platinum</v>
       </c>
       <c r="J114" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B115" s="11">
         <v>36</v>
@@ -2799,12 +3790,12 @@
         <v>Platinum</v>
       </c>
       <c r="J115" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B116" s="11">
         <v>36</v>
@@ -2836,12 +3827,12 @@
         <v>Gold</v>
       </c>
       <c r="J116" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B117" s="11">
         <v>36</v>
@@ -2873,12 +3864,12 @@
         <v>Silver</v>
       </c>
       <c r="J117" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B118" s="11">
         <v>60</v>
@@ -2910,12 +3901,12 @@
         <v>Silver</v>
       </c>
       <c r="J118" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B119" s="42"/>
       <c r="C119" s="42"/>
@@ -2929,7 +3920,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B120" s="11">
         <v>120</v>
@@ -2961,12 +3952,12 @@
         <v>Platinum</v>
       </c>
       <c r="J120" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B121" s="11">
         <v>120</v>
@@ -2998,12 +3989,12 @@
         <v>Platinum</v>
       </c>
       <c r="J121" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B122" s="11">
         <v>120</v>
@@ -3035,12 +4026,12 @@
         <v>Gold</v>
       </c>
       <c r="J122" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B123" s="11">
         <v>120</v>
@@ -3072,12 +4063,12 @@
         <v>Silver</v>
       </c>
       <c r="J123" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B124" s="11">
         <v>120</v>
@@ -3109,12 +4100,12 @@
         <v>Silver</v>
       </c>
       <c r="J124" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B125" s="11">
         <v>60</v>
@@ -3146,12 +4137,12 @@
         <v>Gold</v>
       </c>
       <c r="J125" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -3169,87 +4160,88 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B129" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C129" s="21" t="s">
         <v>165</v>
-      </c>
-      <c r="B129" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C129" s="21" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B130" s="32">
         <v>12</v>
       </c>
       <c r="C130" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B131" s="32">
         <v>60</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B132" s="32">
         <v>12</v>
       </c>
       <c r="C132" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B133" s="44">
         <v>0.3</v>
       </c>
       <c r="C133" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B134" s="32">
         <v>6</v>
       </c>
       <c r="C134" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B135" s="32">
         <v>25</v>
       </c>
       <c r="C135" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>